--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35C.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35C.xlsx
@@ -158,31 +158,31 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>40594911A6B9C6B5688992AB54B6EC65</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>ver nota</t>
+    <t>79A55667F7872B38B9E9571FDCD421E8</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
   </si>
   <si>
     <t>Subdirección Jurídica</t>
   </si>
   <si>
-    <t>10/10/2022</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de abril de 2022 al 30 de junio de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo  por alguna recomendación por  organismos internacionales</t>
+    <t>08/10/2023</t>
+  </si>
+  <si>
+    <t>06/10/2023</t>
+  </si>
+  <si>
+    <t>Del periodo del 01 de julio del 2023 al 30 de septiembre de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo  por alguna recomendación por  organismos internacionales</t>
   </si>
   <si>
     <t>Comité contra las Desapariciones Forzadas</t>
@@ -689,7 +689,7 @@
   <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -933,22 +933,22 @@
         <v>47</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>47</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>47</v>
@@ -957,10 +957,10 @@
         <v>47</v>
       </c>
       <c r="N8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>53</v>
@@ -980,7 +980,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I199">
       <formula1>Hidden_18</formula1>
     </dataValidation>
   </dataValidations>
